--- a/july 2026/GT_JULY_26/07-07-2026/LMT Asif Saab.xlsx
+++ b/july 2026/GT_JULY_26/07-07-2026/LMT Asif Saab.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0814BBE-1B6C-479F-8B58-2D0752D02072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816E37CF-54E4-45C3-9FC1-49AFCEBC9162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="128">
   <si>
     <t>Gm</t>
   </si>
@@ -359,9 +359,6 @@
     <t xml:space="preserve">Address: </t>
   </si>
   <si>
-    <t>Shop Bill Summary (Vacant_01)</t>
-  </si>
-  <si>
     <t>Umair Rehman</t>
   </si>
   <si>
@@ -410,9 +407,6 @@
     <t>Filer &amp; Non Register</t>
   </si>
   <si>
-    <t>Borrow</t>
-  </si>
-  <si>
     <t xml:space="preserve">Customer Name : Waseem Brother Borrow </t>
   </si>
   <si>
@@ -423,6 +417,18 @@
   </si>
   <si>
     <t>Customer Name : NAGINA Food Store</t>
+  </si>
+  <si>
+    <t>Nagina Food</t>
+  </si>
+  <si>
+    <t>Shop Bill Summary (Nagina)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Name : Asif SB </t>
+  </si>
+  <si>
+    <t>Address: Native</t>
   </si>
 </sst>
 </file>
@@ -3129,7 +3135,7 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -3137,7 +3143,7 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -3236,7 +3242,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -3264,7 +3270,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -4457,7 +4463,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -4485,7 +4491,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -5678,7 +5684,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -5706,7 +5712,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -6899,7 +6905,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -6927,7 +6933,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -8120,7 +8126,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -8148,7 +8154,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -9341,7 +9347,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -9369,7 +9375,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -10559,7 +10565,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -10587,7 +10593,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -11776,7 +11782,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -11804,7 +11810,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -12993,7 +12999,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -13021,7 +13027,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -14210,7 +14216,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -14238,7 +14244,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -18177,7 +18183,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -18205,7 +18211,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -19394,7 +19400,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -19422,7 +19428,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -20611,7 +20617,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -20639,7 +20645,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -21828,7 +21834,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -21856,7 +21862,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -22998,7 +23004,7 @@
     <col min="17" max="17" width="4.54296875" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="7.26953125" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="61.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:21 16383:16384" ht="21" x14ac:dyDescent="0.5">
@@ -23050,7 +23056,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -23065,7 +23071,7 @@
     </row>
     <row r="5" spans="1:21 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="215" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B5" s="215"/>
       <c r="C5" s="215"/>
@@ -23078,7 +23084,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -23222,7 +23228,7 @@
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="T12" s="226" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="U12" s="227"/>
       <c r="XFD12" t="s">
@@ -23342,7 +23348,7 @@
       </c>
       <c r="U15" s="164">
         <f>+'2'!P35</f>
-        <v>304948.96704000002</v>
+        <v>0</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -23412,11 +23418,11 @@
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
         <f>+'3'!A5</f>
-        <v xml:space="preserve">Customer Name : </v>
+        <v xml:space="preserve">Customer Name : Asif SB </v>
       </c>
       <c r="U16" s="164">
         <f>+'3'!P35</f>
-        <v>0</v>
+        <v>212.17202237500004</v>
       </c>
       <c r="XFD16" t="s">
         <v>82</v>
@@ -23605,27 +23611,27 @@
       </c>
       <c r="K19" s="172">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
-        <v>6101.76</v>
+        <v>1016.9600000000002</v>
       </c>
       <c r="L19" s="175">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>15109.119999999999</v>
+        <v>3486.72</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>7845.119999999999</v>
+        <v>24552.32</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>27562.521600000004</v>
+        <v>4419.4175999999998</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>903.43820800000015</v>
+        <v>144.858688</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>36311.079808000002</v>
+        <v>29116.596288000001</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23675,27 +23681,27 @@
       </c>
       <c r="K20" s="172">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
-        <v>5593.2800000000007</v>
+        <v>508.48000000000008</v>
       </c>
       <c r="L20" s="175">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>13365.76</v>
+        <v>1743.36</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="2"/>
-        <v>-4431.0400000000009</v>
+        <v>12276.16</v>
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>25352.812800000003</v>
+        <v>2209.7087999999999</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>831.00886400000013</v>
+        <v>72.429344</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>21752.781664000002</v>
+        <v>14558.298144</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23803,11 +23809,11 @@
       <c r="G22" s="114"/>
       <c r="H22" s="172">
         <f>+'1'!H22+'2'!H22+'4'!H22+'3'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22+'17'!H22+'18'!H22+'19'!H22+'20'!H22</f>
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>15692.000000000002</v>
+        <v>15888.150000000001</v>
       </c>
       <c r="J22" s="172">
         <f>+'1'!J22+'2'!J22+'4'!J22+'3'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22+'13'!J22+'14'!J22+'15'!J22+'16'!J22+'17'!J22+'18'!J22+'19'!J22+'20'!J22</f>
@@ -23815,27 +23821,27 @@
       </c>
       <c r="K22" s="172">
         <f>+'1'!K22+'2'!K22+'4'!K22+'3'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22</f>
-        <v>549.22000000000014</v>
+        <v>556.08525000000009</v>
       </c>
       <c r="L22" s="175">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>1584.8920000000001</v>
+        <v>1604.5070000000001</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="2"/>
-        <v>13557.888000000003</v>
+        <v>13727.557750000002</v>
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>2440.4198400000005</v>
+        <v>2477.7471850000006</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>79.99153920000002</v>
+        <v>85.166466575000015</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>16078.299379200003</v>
+        <v>16290.471401575001</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -23993,7 +23999,7 @@
       <c r="B25" s="237"/>
       <c r="C25" s="238">
         <f>H25/40</f>
-        <v>50</v>
+        <v>50.125</v>
       </c>
       <c r="D25" s="232"/>
       <c r="E25" s="232"/>
@@ -24004,11 +24010,11 @@
       </c>
       <c r="H25" s="177">
         <f t="shared" si="3"/>
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="I25" s="178">
         <f t="shared" si="3"/>
-        <v>119809.5</v>
+        <v>120005.65</v>
       </c>
       <c r="J25" s="177">
         <f t="shared" si="3"/>
@@ -24016,27 +24022,27 @@
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
-        <v>14362.932500000001</v>
+        <v>4200.1977500000003</v>
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>37323.792000000001</v>
+        <v>14098.606999999998</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>68122.775500000003</v>
+        <v>101706.84525000001</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>64562.899590000015</v>
+        <v>18314.018935</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>2116.2283754500004</v>
+        <v>604.24426282500008</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>134801.90346545001</v>
+        <v>120625.10844782501</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24276,7 +24282,7 @@
       </c>
       <c r="U34" s="165">
         <f>SUM(U14:U33)</f>
-        <v>425361.90346545004</v>
+        <v>120625.108447825</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24309,7 +24315,7 @@
       <c r="O36" s="249"/>
       <c r="P36" s="152">
         <f>I25</f>
-        <v>119809.5</v>
+        <v>120005.65</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24330,7 +24336,7 @@
       <c r="O37" s="251"/>
       <c r="P37" s="153">
         <f>L25</f>
-        <v>37323.792000000001</v>
+        <v>14098.606999999998</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24351,7 +24357,7 @@
       <c r="O38" s="251"/>
       <c r="P38" s="154">
         <f>K25</f>
-        <v>14362.932500000001</v>
+        <v>4200.1977500000003</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24373,7 +24379,7 @@
       <c r="O39" s="251"/>
       <c r="P39" s="153">
         <f>P36-P37-P38</f>
-        <v>68122.775500000003</v>
+        <v>101706.84524999998</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24398,7 +24404,7 @@
       </c>
       <c r="P40" s="153">
         <f>N25</f>
-        <v>64562.899590000015</v>
+        <v>18314.018935</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24420,7 +24426,7 @@
       <c r="O41" s="253"/>
       <c r="P41" s="153">
         <f>P39+P40</f>
-        <v>132685.67509000003</v>
+        <v>120020.86418499998</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24445,7 +24451,7 @@
       </c>
       <c r="P42" s="153">
         <f>O42*P41</f>
-        <v>3317.141877250001</v>
+        <v>3000.5216046249998</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24455,7 +24461,7 @@
       <c r="O43" s="231"/>
       <c r="P43" s="160">
         <f>P41+P42</f>
-        <v>136002.81696725002</v>
+        <v>123021.38578962498</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24635,7 +24641,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -24650,7 +24656,7 @@
     </row>
     <row r="5" spans="1:26 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="257" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B5" s="257"/>
       <c r="C5" s="257"/>
@@ -24663,7 +24669,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -24672,7 +24678,7 @@
     </row>
     <row r="6" spans="1:26 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="212" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B6" s="212"/>
       <c r="C6" s="212"/>
@@ -24884,13 +24890,13 @@
         <v>74</v>
       </c>
       <c r="S14" s="264" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="T14" s="264"/>
       <c r="U14" s="264"/>
       <c r="V14" s="264"/>
       <c r="W14" s="265" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X14" s="265"/>
       <c r="Y14" s="265"/>
@@ -24941,28 +24947,28 @@
         <v>1</v>
       </c>
       <c r="S15" s="185" t="s">
+        <v>109</v>
+      </c>
+      <c r="T15" s="185" t="s">
         <v>110</v>
       </c>
-      <c r="T15" s="185" t="s">
-        <v>111</v>
-      </c>
       <c r="U15" s="185" t="s">
+        <v>114</v>
+      </c>
+      <c r="V15" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="V15" s="185" t="s">
-        <v>116</v>
-      </c>
       <c r="W15" s="186" t="s">
+        <v>109</v>
+      </c>
+      <c r="X15" s="186" t="s">
         <v>110</v>
       </c>
-      <c r="X15" s="186" t="s">
-        <v>111</v>
-      </c>
       <c r="Y15" s="186" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z15" s="186" t="s">
         <v>115</v>
-      </c>
-      <c r="Z15" s="186" t="s">
-        <v>116</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -25027,26 +25033,26 @@
       </c>
       <c r="Q16" s="108"/>
       <c r="S16" s="183" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T16" s="183">
         <v>1697</v>
       </c>
       <c r="U16" s="183" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V16" s="183">
         <f>T16/40</f>
         <v>42.424999999999997</v>
       </c>
       <c r="W16" s="187" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X16" s="187">
         <v>1664</v>
       </c>
       <c r="Y16" s="187" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Z16" s="187">
         <f>X16/40</f>
@@ -25114,26 +25120,26 @@
         <v>10514.382108750002</v>
       </c>
       <c r="S17" s="184" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T17" s="183">
         <v>2322</v>
       </c>
       <c r="U17" s="183" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="V17" s="183">
         <f t="shared" ref="V17:V18" si="7">T17/40</f>
         <v>58.05</v>
       </c>
       <c r="W17" s="188" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X17" s="187">
         <v>2277</v>
       </c>
       <c r="Y17" s="187" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Z17" s="187">
         <f t="shared" ref="Z17:Z18" si="8">X17/40</f>
@@ -25199,26 +25205,26 @@
         <v>0</v>
       </c>
       <c r="S18" s="183" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T18" s="183">
         <v>3216</v>
       </c>
       <c r="U18" s="183" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V18" s="183">
         <f t="shared" si="7"/>
         <v>80.400000000000006</v>
       </c>
       <c r="W18" s="187" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X18" s="187">
         <v>3153</v>
       </c>
       <c r="Y18" s="187" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z18" s="187">
         <f t="shared" si="8"/>
@@ -25283,13 +25289,13 @@
         <v>29116.596288000001</v>
       </c>
       <c r="S19" s="266" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="T19" s="266"/>
       <c r="U19" s="266"/>
       <c r="V19" s="266"/>
       <c r="W19" s="267" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X19" s="267"/>
       <c r="Y19" s="267"/>
@@ -25353,28 +25359,28 @@
         <v>14558.298144</v>
       </c>
       <c r="S20" s="185" t="s">
+        <v>109</v>
+      </c>
+      <c r="T20" s="185" t="s">
         <v>110</v>
       </c>
-      <c r="T20" s="185" t="s">
-        <v>111</v>
-      </c>
       <c r="U20" s="185" t="s">
+        <v>114</v>
+      </c>
+      <c r="V20" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="V20" s="185" t="s">
-        <v>116</v>
-      </c>
       <c r="W20" s="185" t="s">
+        <v>109</v>
+      </c>
+      <c r="X20" s="185" t="s">
         <v>110</v>
       </c>
-      <c r="X20" s="185" t="s">
-        <v>111</v>
-      </c>
       <c r="Y20" s="185" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z20" s="185" t="s">
         <v>115</v>
-      </c>
-      <c r="Z20" s="185" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:26 16384:16384" x14ac:dyDescent="0.35">
@@ -25435,26 +25441,26 @@
         <v>29116.596288000001</v>
       </c>
       <c r="S21" s="189" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T21" s="189">
         <v>1610</v>
       </c>
       <c r="U21" s="189" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V21" s="189">
         <f>T21/40</f>
         <v>40.25</v>
       </c>
       <c r="W21" s="191" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X21" s="191">
         <v>1642</v>
       </c>
       <c r="Y21" s="191" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Z21" s="191">
         <f>X21/40</f>
@@ -25519,26 +25525,26 @@
         <v>16078.299379200003</v>
       </c>
       <c r="S22" s="190" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T22" s="189">
         <v>2202</v>
       </c>
       <c r="U22" s="189" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="V22" s="189">
         <f t="shared" ref="V22:V25" si="9">T22/40</f>
         <v>55.05</v>
       </c>
       <c r="W22" s="192" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X22" s="191">
         <v>2246</v>
       </c>
       <c r="Y22" s="191" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Z22" s="191">
         <f t="shared" ref="Z22:Z25" si="10">X22/40</f>
@@ -25601,26 +25607,26 @@
         <v>0</v>
       </c>
       <c r="S23" s="189" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T23" s="189">
         <v>3216</v>
       </c>
       <c r="U23" s="189" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V23" s="189">
         <f t="shared" si="9"/>
         <v>80.400000000000006</v>
       </c>
       <c r="W23" s="191" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X23" s="191">
         <v>3216</v>
       </c>
       <c r="Y23" s="191" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Z23" s="191">
         <f t="shared" si="10"/>
@@ -25683,13 +25689,13 @@
         <v>0</v>
       </c>
       <c r="S24" s="189" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T24" s="189">
         <v>3216</v>
       </c>
       <c r="U24" s="189" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V24" s="189">
         <f t="shared" si="9"/>
@@ -25698,7 +25704,7 @@
       <c r="W24" s="191"/>
       <c r="X24" s="191"/>
       <c r="Y24" s="191" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Z24" s="191">
         <f t="shared" si="10"/>
@@ -25752,26 +25758,26 @@
         <v>120412.93642545001</v>
       </c>
       <c r="S25" s="189" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T25" s="189">
         <v>3216</v>
       </c>
       <c r="U25" s="189" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V25" s="189">
         <f t="shared" si="9"/>
         <v>80.400000000000006</v>
       </c>
       <c r="W25" s="191" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X25" s="191">
         <v>3110</v>
       </c>
       <c r="Y25" s="191" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z25" s="191">
         <f t="shared" si="10"/>
@@ -26147,7 +26153,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -26162,7 +26168,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="257" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B5" s="257"/>
       <c r="C5" s="257"/>
@@ -26175,7 +26181,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -26184,7 +26190,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="212" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B6" s="212"/>
       <c r="C6" s="212"/>
@@ -26649,33 +26655,32 @@
       </c>
       <c r="H19" s="115"/>
       <c r="I19" s="116">
-        <f t="shared" si="2"/>
-        <v>145280</v>
+        <v>0</v>
       </c>
       <c r="J19" s="117"/>
       <c r="K19" s="104">
         <f t="shared" si="3"/>
-        <v>5084.8</v>
+        <v>0</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
-        <v>11622.4</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>128572.80000000002</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>23143.104000000003</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>758.57952000000012</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>152474.48352000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26707,33 +26712,32 @@
       </c>
       <c r="H20" s="115"/>
       <c r="I20" s="116">
-        <f t="shared" si="2"/>
-        <v>145280</v>
+        <v>0</v>
       </c>
       <c r="J20" s="117"/>
       <c r="K20" s="104">
         <f t="shared" si="3"/>
-        <v>5084.8</v>
+        <v>0</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
-        <v>11622.4</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>128572.80000000002</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>23143.104000000003</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>758.57952000000012</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>152474.48352000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26979,32 +26983,32 @@
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>290560</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>10169.6</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>23244.799999999999</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>257145.60000000003</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>46286.208000000006</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>1517.1590400000002</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>304948.96704000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27054,7 +27058,7 @@
       <c r="O28" s="249"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>290560</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27075,7 +27079,7 @@
       <c r="O29" s="251"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>23244.799999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27096,7 +27100,7 @@
       <c r="O30" s="251"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>10169.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27118,7 +27122,7 @@
       <c r="O31" s="251"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>257145.60000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27143,7 +27147,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>46286.208000000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27165,7 +27169,7 @@
       <c r="O33" s="253"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>303431.80800000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27190,7 +27194,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>1517.1590400000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27200,7 +27204,7 @@
       <c r="O35" s="231"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>304948.96704000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27372,7 +27376,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -27387,7 +27391,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="257" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="B5" s="257"/>
       <c r="C5" s="257"/>
@@ -27400,7 +27404,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -27409,7 +27413,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="212" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="B6" s="212"/>
       <c r="C6" s="212"/>
@@ -27421,7 +27425,7 @@
       <c r="L6" s="212"/>
       <c r="M6" s="212"/>
       <c r="N6" s="214" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="O6" s="214"/>
       <c r="P6" s="214"/>
@@ -27517,11 +27521,11 @@
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
       <c r="A11" s="217"/>
       <c r="B11" s="76" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C11" s="77" t="str">
         <f>IF($O34&gt;2.49%,"No","Yes")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
@@ -27660,7 +27664,7 @@
       </c>
       <c r="O15" s="93">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>5.0000000000000001E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="P15" s="94" t="s">
         <v>1</v>
@@ -28038,35 +28042,37 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115"/>
+      <c r="H22" s="115">
+        <v>5</v>
+      </c>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>196.15000000000003</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>0</v>
+        <v>6.8652500000000014</v>
       </c>
       <c r="L22" s="120">
         <f>I22*10%</f>
-        <v>0</v>
+        <v>19.615000000000006</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>169.66975000000002</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>37.327345000000008</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5.1749273750000011</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>212.17202237500004</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28196,36 +28202,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>196.15000000000003</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>6.8652500000000014</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>19.615000000000006</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>169.66975000000002</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>0</v>
+        <v>37.327345000000008</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>0</v>
+        <v>5.1749273750000011</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>0</v>
+        <v>212.17202237500004</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28275,7 +28281,7 @@
       <c r="O28" s="249"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>0</v>
+        <v>196.15000000000003</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28296,7 +28302,7 @@
       <c r="O29" s="251"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>0</v>
+        <v>19.615000000000006</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28317,7 +28323,7 @@
       <c r="O30" s="251"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>0</v>
+        <v>6.8652500000000014</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28339,7 +28345,7 @@
       <c r="O31" s="251"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>0</v>
+        <v>169.66975000000002</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28364,7 +28370,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>0</v>
+        <v>37.327345000000008</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28386,7 +28392,7 @@
       <c r="O33" s="253"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>0</v>
+        <v>206.99709500000003</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28407,11 +28413,11 @@
       </c>
       <c r="O34" s="159">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>5.0000000000000001E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>0</v>
+        <v>5.1749273750000011</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28421,7 +28427,7 @@
       <c r="O35" s="231"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>0</v>
+        <v>212.17202237500004</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -28501,7 +28507,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -28592,7 +28598,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -28620,7 +28626,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -29813,7 +29819,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -29841,7 +29847,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -31034,7 +31040,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -31062,7 +31068,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
